--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260618.xlsx
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
